--- a/NVDA_Model.xlsx
+++ b/NVDA_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859D5FF4-F733-4D15-A7C8-BB63C9C062D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1BB626-08C4-497D-BC39-735C5A5F6C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="12435" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -5014,9 +5014,6 @@
     <t xml:space="preserve">IPO: Jan 22, 1999 </t>
   </si>
   <si>
-    <t>8/27/2025</t>
-  </si>
-  <si>
     <t>Revenue</t>
   </si>
   <si>
@@ -5366,6 +5363,9 @@
   </si>
   <si>
     <t>Customers use Singapore to centralize invoicing while products are almost always shipped elsewhere. Over 99% of controlled Data Center compute revenue billed to Singapore was for orders from U.S.-based customers</t>
+  </si>
+  <si>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -15804,14 +15804,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:S98"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="11.59765625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.1328125" style="1"/>
+    <col min="1" max="1" width="3.42578125" style="1" customWidth="1"/>
+    <col min="2" max="4" width="11.5703125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="13.9">
+    <row r="2" spans="2:19" ht="15">
       <c r="B2" s="2" t="s">
         <v>165</v>
       </c>
@@ -15821,10 +15821,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="47">
-        <v>193.25</v>
+        <v>182.54</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>1605</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="4" spans="2:19">
@@ -15835,7 +15835,7 @@
         <v>24327</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="5" spans="2:19">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="C5" s="46">
         <f>C3*C4</f>
-        <v>4701192.75</v>
+        <v>4440650.58</v>
       </c>
     </row>
     <row r="6" spans="2:19">
@@ -15855,7 +15855,7 @@
         <v>60608</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="7" spans="2:19">
@@ -15867,7 +15867,7 @@
         <v>8467</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="8" spans="2:19">
@@ -15876,10 +15876,10 @@
       </c>
       <c r="C8" s="46">
         <f>C5-C6+C7</f>
-        <v>4649051.75</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" ht="13.9">
+        <v>4388509.58</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" ht="15">
       <c r="B10" s="2" t="s">
         <v>166</v>
       </c>
@@ -16004,15 +16004,15 @@
         <v>160</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="13.9">
+    <row r="20" spans="1:18" ht="15">
       <c r="N20" s="2"/>
     </row>
-    <row r="21" spans="1:18" ht="13.9">
+    <row r="21" spans="1:18" ht="15">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="13.9">
+    <row r="22" spans="1:18" ht="15">
       <c r="B22" s="1" t="s">
         <v>168</v>
       </c>
@@ -16022,7 +16022,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="13.9">
+    <row r="24" spans="1:18" ht="15">
       <c r="C24" s="1" t="s">
         <v>170</v>
       </c>
@@ -16037,7 +16037,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="13.9">
+    <row r="27" spans="1:18" ht="15">
       <c r="C27" s="2" t="s">
         <v>171</v>
       </c>
@@ -16082,7 +16082,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="13.9">
+    <row r="37" spans="1:4" ht="15">
       <c r="A37" s="2" t="s">
         <v>163</v>
       </c>
@@ -16114,7 +16114,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="B43" s="1" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -16122,7 +16122,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="13.9">
+    <row r="46" spans="1:4" ht="15">
       <c r="B46" s="2" t="s">
         <v>189</v>
       </c>
@@ -16187,7 +16187,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="59" spans="3:5" ht="13.9">
+    <row r="59" spans="3:5" ht="15">
       <c r="D59" s="1" t="s">
         <v>218</v>
       </c>
@@ -16232,7 +16232,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="2:18" ht="13.9">
+    <row r="68" spans="2:18" ht="15">
       <c r="B68" s="2" t="s">
         <v>210</v>
       </c>
@@ -16300,7 +16300,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="81" spans="2:4" ht="13.9">
+    <row r="81" spans="2:4" ht="15">
       <c r="B81" s="2" t="s">
         <v>248</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="91" spans="2:4" ht="13.9">
+    <row r="91" spans="2:4" ht="15">
       <c r="B91" s="2" t="s">
         <v>258</v>
       </c>
@@ -16410,23 +16410,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B27957-A42B-4AB7-A411-12A70E029F5D}">
   <dimension ref="B1:FB107"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="3.1328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.3984375" style="1" customWidth="1"/>
-    <col min="3" max="18" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="67" width="9.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="9.1328125" style="1"/>
-    <col min="69" max="74" width="9.1328125" style="35"/>
-    <col min="75" max="95" width="9.1328125" style="1"/>
-    <col min="96" max="104" width="9.1328125" style="35" customWidth="1"/>
-    <col min="105" max="105" width="9.73046875" style="35" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" style="1" customWidth="1"/>
+    <col min="3" max="18" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="67" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="9.140625" style="1"/>
+    <col min="69" max="74" width="9.140625" style="35"/>
+    <col min="75" max="95" width="9.140625" style="1"/>
+    <col min="96" max="104" width="9.140625" style="35" customWidth="1"/>
+    <col min="105" max="105" width="9.7109375" style="35" customWidth="1"/>
     <col min="106" max="106" width="9" style="35" customWidth="1"/>
-    <col min="107" max="155" width="9.1328125" style="35"/>
-    <col min="156" max="16384" width="9.1328125" style="1"/>
+    <col min="107" max="155" width="9.140625" style="35"/>
+    <col min="156" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:158" ht="13.9">
+    <row r="1" spans="2:158" ht="15">
       <c r="B1" s="1" t="s">
         <v>115</v>
       </c>
@@ -16462,9 +16462,9 @@
       </c>
       <c r="BW2" s="35"/>
     </row>
-    <row r="3" spans="2:158" ht="13.9">
+    <row r="3" spans="2:158" ht="15">
       <c r="B3" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="C3" s="33" t="s">
         <v>43</v>
@@ -17168,7 +17168,7 @@
         <v>182830.70955253564</v>
       </c>
     </row>
-    <row r="6" spans="2:158" s="2" customFormat="1" ht="13.9">
+    <row r="6" spans="2:158" s="2" customFormat="1" ht="15">
       <c r="B6" s="33" t="s">
         <v>188</v>
       </c>
@@ -18097,7 +18097,7 @@
         <v>4600.4856090606345</v>
       </c>
     </row>
-    <row r="11" spans="2:158" s="2" customFormat="1" ht="13.9">
+    <row r="11" spans="2:158" s="2" customFormat="1" ht="15">
       <c r="B11" s="33" t="s">
         <v>118</v>
       </c>
@@ -18499,7 +18499,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="15" spans="2:158" s="2" customFormat="1" ht="13.9">
+    <row r="15" spans="2:158" s="2" customFormat="1" ht="15">
       <c r="B15" s="33" t="s">
         <v>1533</v>
       </c>
@@ -19399,7 +19399,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="20" spans="2:155" s="2" customFormat="1" ht="13.9">
+    <row r="20" spans="2:155" s="2" customFormat="1" ht="15">
       <c r="B20" s="33" t="s">
         <v>1537</v>
       </c>
@@ -21094,7 +21094,7 @@
         <v>7875</v>
       </c>
     </row>
-    <row r="33" spans="2:155" s="2" customFormat="1" ht="13.9">
+    <row r="33" spans="2:155" s="2" customFormat="1" ht="15">
       <c r="B33" s="2" t="s">
         <v>118</v>
       </c>
@@ -21949,7 +21949,7 @@
         <v>1.3066783831282951</v>
       </c>
     </row>
-    <row r="40" spans="2:155" s="2" customFormat="1" ht="13.9">
+    <row r="40" spans="2:155" s="2" customFormat="1" ht="15">
       <c r="B40" s="2" t="s">
         <v>1555</v>
       </c>
@@ -22946,7 +22946,7 @@
     <row r="47" spans="2:155">
       <c r="BQ47" s="1"/>
     </row>
-    <row r="48" spans="2:155" s="2" customFormat="1" ht="13.9">
+    <row r="48" spans="2:155" s="2" customFormat="1" ht="15">
       <c r="B48" s="2" t="s">
         <v>117</v>
       </c>
@@ -26992,7 +26992,7 @@
         <v>365843.47033225169</v>
       </c>
     </row>
-    <row r="60" spans="2:155" s="2" customFormat="1" ht="13.9">
+    <row r="60" spans="2:155" s="2" customFormat="1" ht="15">
       <c r="B60" s="2" t="s">
         <v>138</v>
       </c>
@@ -31505,7 +31505,7 @@
         <v>24327</v>
       </c>
       <c r="DB81" s="74" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="82" spans="2:155" s="2" customFormat="1" ht="15" customHeight="1">
@@ -31696,7 +31696,7 @@
       </c>
       <c r="DA83" s="70">
         <f>Main!C3</f>
-        <v>193.25</v>
+        <v>182.54</v>
       </c>
       <c r="DB83" s="73" t="s">
         <v>167</v>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="DA84" s="66">
         <f>DA82/DA83-1</f>
-        <v>0.15045073160361166</v>
+        <v>0.21795005961651115</v>
       </c>
       <c r="DB84" s="75" t="str">
         <f>IF(DA84&gt;0,"Upside","Downside")</f>
@@ -32235,7 +32235,7 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="90" spans="2:155" s="2" customFormat="1" ht="13.9">
+    <row r="90" spans="2:155" s="2" customFormat="1" ht="15">
       <c r="B90" s="2" t="s">
         <v>1585</v>
       </c>
@@ -32487,7 +32487,7 @@
         <v>79327</v>
       </c>
     </row>
-    <row r="92" spans="2:155" s="2" customFormat="1" ht="13.9">
+    <row r="92" spans="2:155" s="2" customFormat="1" ht="15">
       <c r="B92" s="2" t="s">
         <v>1587</v>
       </c>
@@ -33734,7 +33734,7 @@
         <v>72880</v>
       </c>
     </row>
-    <row r="103" spans="2:155" s="2" customFormat="1" ht="13.9">
+    <row r="103" spans="2:155" s="2" customFormat="1" ht="15">
       <c r="B103" s="2" t="s">
         <v>139</v>
       </c>
@@ -34343,7 +34343,7 @@
         <v>-3236</v>
       </c>
     </row>
-    <row r="105" spans="2:155" s="2" customFormat="1" ht="13.9">
+    <row r="105" spans="2:155" s="2" customFormat="1" ht="15">
       <c r="B105" s="2" t="s">
         <v>141</v>
       </c>
@@ -35463,13 +35463,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{714FD4A5-C172-4508-BDD9-9132B91E029B}">
   <dimension ref="A1:CD1616"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="7" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="3.1328125" style="1" customWidth="1"/>
-    <col min="9" max="31" width="9.1328125" style="1"/>
-    <col min="32" max="32" width="2.86328125" style="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.1328125" style="1"/>
+    <col min="8" max="8" width="3.140625" style="1" customWidth="1"/>
+    <col min="9" max="31" width="9.140625" style="1"/>
+    <col min="32" max="32" width="2.85546875" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="8:82">
@@ -35477,25 +35477,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="8:82" ht="13.9">
+    <row r="2" spans="8:82" ht="15">
       <c r="H2" s="2" t="s">
         <v>164</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>1656</v>
-      </c>
-    </row>
-    <row r="4" spans="8:82" ht="14.25">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="4" spans="8:82" ht="15">
       <c r="AG4"/>
     </row>
     <row r="21" spans="41:41">
       <c r="AO21" s="1" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="32" spans="41:41">
       <c r="AO32" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="34" spans="8:33">
@@ -35516,15 +35516,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="8:33" ht="13.9">
+    <row r="37" spans="8:33" ht="15">
       <c r="H37" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>1657</v>
-      </c>
-    </row>
-    <row r="38" spans="8:33" ht="13.9">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="38" spans="8:33" ht="15">
       <c r="AG38" s="2" t="s">
         <v>144</v>
       </c>
@@ -35547,7 +35547,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="8:10" ht="13.9">
+    <row r="69" spans="8:10" ht="15">
       <c r="H69" s="2" t="s">
         <v>1531</v>
       </c>
@@ -35557,22 +35557,22 @@
         <v>14</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="102" spans="8:11">
       <c r="J102" s="1" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="103" spans="8:11">
       <c r="K103" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="104" spans="8:11">
       <c r="K104" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="105" spans="8:11">
@@ -35580,9 +35580,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="8:11" ht="13.9">
+    <row r="107" spans="8:11" ht="15">
       <c r="H107" s="2" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="139" spans="9:11">
@@ -35590,40 +35590,40 @@
         <v>14</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="140" spans="9:11">
       <c r="K140" s="1" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="141" spans="9:11">
       <c r="K141" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="142" spans="9:11">
       <c r="J142" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="143" spans="9:11">
       <c r="K143" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="144" spans="9:11">
       <c r="J144" s="1" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="145" spans="8:33">
       <c r="K145" s="1" t="s">
-        <v>1654</v>
-      </c>
-    </row>
-    <row r="147" spans="8:33" ht="13.9">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="147" spans="8:33" ht="15">
       <c r="H147" s="2" t="s">
         <v>273</v>
       </c>
@@ -35649,12 +35649,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="8:10" ht="13.9">
+    <row r="180" spans="8:10" ht="15">
       <c r="H180" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="13.9">
+    <row r="198" spans="1:7">
       <c r="A198" s="1" t="s">
         <v>1529</v>
       </c>
@@ -36796,7 +36796,7 @@
         <v>0.15613307715643643</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="13.9">
+    <row r="245" spans="1:33" ht="15">
       <c r="A245" s="49">
         <v>122.99145595998885</v>
       </c>
@@ -36863,7 +36863,7 @@
         <v>1.1135857461024301E-3</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="13.9">
+    <row r="247" spans="1:33" ht="15">
       <c r="A247" s="49">
         <v>117.36184704084465</v>
       </c>
@@ -36896,7 +36896,7 @@
       </c>
       <c r="M247" s="2"/>
     </row>
-    <row r="248" spans="1:33" ht="13.9">
+    <row r="248" spans="1:33" ht="15">
       <c r="A248" s="49">
         <v>117.05186857460403</v>
       </c>
@@ -36932,7 +36932,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="13.9">
+    <row r="249" spans="1:33" ht="15">
       <c r="A249" s="49">
         <v>113.53211308696858</v>
       </c>
@@ -37015,7 +37015,7 @@
         <v>2.8025923979679845E-3</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="13.9">
+    <row r="252" spans="1:33">
       <c r="A252" s="49">
         <v>111.60224715198663</v>
       </c>
@@ -37045,7 +37045,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="13.9" thickBot="1">
+    <row r="253" spans="1:33" ht="15" thickBot="1">
       <c r="A253" s="49">
         <v>108.91243400944704</v>
       </c>
@@ -37120,7 +37120,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="14.25">
+    <row r="255" spans="1:33" ht="15">
       <c r="A255" s="49">
         <v>108.72244720755764</v>
       </c>
@@ -37167,7 +37167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="14.25">
+    <row r="256" spans="1:33" ht="15">
       <c r="A256" s="49">
         <v>111.0022888302306</v>
       </c>
@@ -37211,7 +37211,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="257" spans="1:17" ht="14.25">
+    <row r="257" spans="1:17" ht="15">
       <c r="A257" s="49">
         <v>106.42260697415946</v>
       </c>
@@ -37258,7 +37258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:17" ht="14.25">
+    <row r="258" spans="1:17" ht="15">
       <c r="A258" s="49">
         <v>102.70286537927198</v>
       </c>
@@ -37303,7 +37303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:17" ht="14.25">
+    <row r="259" spans="1:17" ht="15">
       <c r="A259" s="49">
         <v>98.883130730758523</v>
       </c>
@@ -37350,7 +37350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:17" ht="14.25">
+    <row r="260" spans="1:17" ht="15">
       <c r="A260" s="49">
         <v>96.903268268963572</v>
       </c>
@@ -37396,7 +37396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:17" ht="14.25">
+    <row r="261" spans="1:17" ht="15">
       <c r="A261" s="49">
         <v>101.48295012503471</v>
       </c>
@@ -37444,7 +37444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:17" ht="14.25">
+    <row r="262" spans="1:17" ht="15">
       <c r="A262" s="49">
         <v>104.48274173381492</v>
       </c>
@@ -37489,7 +37489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="263" spans="1:17" ht="14.25">
+    <row r="263" spans="1:17" ht="15">
       <c r="A263" s="49">
         <v>112.19220616838008</v>
       </c>
@@ -37537,7 +37537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:17" ht="14.25">
+    <row r="264" spans="1:17" ht="15">
       <c r="A264" s="49">
         <v>110.70230966935256</v>
       </c>
@@ -37582,7 +37582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:17" ht="14.25">
+    <row r="265" spans="1:17" ht="15">
       <c r="A265" s="49">
         <v>110.9222943873298</v>
       </c>
@@ -37630,7 +37630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:17" ht="14.25">
+    <row r="266" spans="1:17" ht="15">
       <c r="A266" s="49">
         <v>107.56252778549594</v>
       </c>
@@ -37675,7 +37675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="1:17" ht="14.25">
+    <row r="267" spans="1:17" ht="15">
       <c r="A267" s="49">
         <v>114.32205821061403</v>
       </c>
@@ -37723,7 +37723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:17" ht="14.25">
+    <row r="268" spans="1:17" ht="15">
       <c r="A268" s="49">
         <v>96.293310641844926</v>
       </c>
@@ -37769,7 +37769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:17" ht="14.25">
+    <row r="269" spans="1:17" ht="15">
       <c r="A269" s="49">
         <v>97.633217560433437</v>
       </c>
@@ -37807,7 +37807,7 @@
         <v>2.4587525271664981</v>
       </c>
     </row>
-    <row r="270" spans="1:17" ht="14.25">
+    <row r="270" spans="1:17" ht="15">
       <c r="A270" s="49">
         <v>94.30344887468739</v>
       </c>
@@ -37845,7 +37845,7 @@
         <v>2.9196448316534065</v>
       </c>
     </row>
-    <row r="271" spans="1:17" ht="14.25">
+    <row r="271" spans="1:17" ht="15">
       <c r="A271" s="49">
         <v>101.79292859127533</v>
       </c>
@@ -37883,7 +37883,7 @@
         <v>3.4371328374098877</v>
       </c>
     </row>
-    <row r="272" spans="1:17" ht="14.25">
+    <row r="272" spans="1:17" ht="15">
       <c r="A272" s="49">
         <v>110.41232981383715</v>
       </c>
@@ -37921,7 +37921,7 @@
         <v>4.0115637582132244</v>
       </c>
     </row>
-    <row r="273" spans="1:13" ht="14.25">
+    <row r="273" spans="1:13" ht="15">
       <c r="A273" s="49">
         <v>110.14234856904693</v>
       </c>
@@ -37959,7 +37959,7 @@
         <v>4.6417545319960221</v>
       </c>
     </row>
-    <row r="274" spans="1:13" ht="14.25">
+    <row r="274" spans="1:13" ht="15">
       <c r="A274" s="49">
         <v>108.37247151986659</v>
       </c>
@@ -37997,7 +37997,7 @@
         <v>5.3247807471385737</v>
       </c>
     </row>
-    <row r="275" spans="1:13" ht="14.25">
+    <row r="275" spans="1:13" ht="15">
       <c r="A275" s="49">
         <v>109.6623819116421</v>
       </c>
@@ -38035,7 +38035,7 @@
         <v>6.0558119237460186</v>
       </c>
     </row>
-    <row r="276" spans="1:13" ht="14.25">
+    <row r="276" spans="1:13" ht="15">
       <c r="A276" s="49">
         <v>111.42225965545983</v>
       </c>
@@ -38073,7 +38073,7 @@
         <v>6.8280094952152028</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="14.25">
+    <row r="277" spans="1:13" ht="15">
       <c r="A277" s="49">
         <v>113.75209780494579</v>
       </c>
@@ -38111,7 +38111,7 @@
         <v>7.6325022832674865</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="14.25">
+    <row r="278" spans="1:13" ht="15">
       <c r="A278" s="49">
         <v>120.68161642122809</v>
       </c>
@@ -38149,7 +38149,7 @@
         <v>8.4584513991785624</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="14.25">
+    <row r="279" spans="1:13" ht="15">
       <c r="A279" s="49">
         <v>121.40156640733534</v>
       </c>
@@ -38187,7 +38187,7 @@
         <v>9.2932123847651589</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="14.25">
+    <row r="280" spans="1:13" ht="15">
       <c r="A280" s="49">
         <v>117.69182411781048</v>
       </c>
@@ -38225,7 +38225,7 @@
         <v>10.122597199307945</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="14.25">
+    <row r="281" spans="1:13" ht="15">
       <c r="A281" s="49">
         <v>118.52176646290634</v>
       </c>
@@ -38263,7 +38263,7 @@
         <v>10.93123265336709</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="14.25">
+    <row r="282" spans="1:13" ht="15">
       <c r="A282" s="49">
         <v>117.51183662128366</v>
       </c>
@@ -38301,7 +38301,7 @@
         <v>11.703005483437979</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="14.25">
+    <row r="283" spans="1:13" ht="15">
       <c r="A283" s="49">
         <v>115.42198180050012</v>
       </c>
@@ -38339,7 +38339,7 @@
         <v>12.421577927161115</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="14.25">
+    <row r="284" spans="1:13" ht="15">
       <c r="A284" s="49">
         <v>119.52169699916641</v>
       </c>
@@ -38377,7 +38377,7 @@
         <v>13.070951911898533</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="14.25">
+    <row r="285" spans="1:13" ht="15">
       <c r="A285" s="49">
         <v>121.66154834676296</v>
       </c>
@@ -38415,7 +38415,7 @@
         <v>13.63605531793295</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="14.25">
+    <row r="286" spans="1:13" ht="15">
       <c r="A286" s="49">
         <v>115.57197138093912</v>
       </c>
@@ -38453,7 +38453,7 @@
         <v>14.103320672840823</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="14.25">
+    <row r="287" spans="1:13" ht="15">
       <c r="A287" s="49">
         <v>115.73196026674073</v>
       </c>
@@ -38491,7 +38491,7 @@
         <v>14.461225422795078</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="14.25">
+    <row r="288" spans="1:13" ht="15">
       <c r="A288" s="49">
         <v>108.74244581828279</v>
       </c>
@@ -38529,7 +38529,7 @@
         <v>14.700763811971989</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="14.25">
+    <row r="289" spans="1:13" ht="15">
       <c r="A289" s="49">
         <v>106.96273311548265</v>
       </c>
@@ -38567,7 +38567,7 @@
         <v>14.81582341284042</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="14.25">
+    <row r="290" spans="1:13" ht="15">
       <c r="A290" s="49">
         <v>112.67181150480219</v>
       </c>
@@ -38605,7 +38605,7 @@
         <v>14.8034443345085</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="14.25">
+    <row r="291" spans="1:13" ht="15">
       <c r="A291" s="49">
         <v>110.55215367899528</v>
       </c>
@@ -38643,7 +38643,7 @@
         <v>14.663945764292501</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="14.25">
+    <row r="292" spans="1:13" ht="15">
       <c r="A292" s="49">
         <v>117.28106743733514</v>
       </c>
@@ -38681,7 +38681,7 @@
         <v>14.400912290249785</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="14.25">
+    <row r="293" spans="1:13" ht="15">
       <c r="A293" s="49">
         <v>115.971278875162</v>
       </c>
@@ -38719,7 +38719,7 @@
         <v>14.021040822857749</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="14.25">
+    <row r="294" spans="1:13" ht="15">
       <c r="A294" s="49">
         <v>114.04159038280007</v>
       </c>
@@ -38757,7 +38757,7 @@
         <v>13.533857241713354</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="14.25">
+    <row r="295" spans="1:13" ht="15">
       <c r="A295" s="49">
         <v>124.89983754707508</v>
       </c>
@@ -38795,7 +38795,7 @@
         <v>12.951319503326856</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="14.25">
+    <row r="296" spans="1:13" ht="15">
       <c r="A296" s="49">
         <v>120.13060743900954</v>
       </c>
@@ -38833,7 +38833,7 @@
         <v>12.287330289013523</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="14.25">
+    <row r="297" spans="1:13" ht="15">
       <c r="A297" s="49">
         <v>131.2588110244958</v>
       </c>
@@ -38871,7 +38871,7 @@
         <v>11.557186894718265</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="14.25">
+    <row r="298" spans="1:13" ht="15">
       <c r="A298" s="49">
         <v>126.60956154807971</v>
       </c>
@@ -38909,7 +38909,7 @@
         <v>10.776998670711615</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="14.25">
+    <row r="299" spans="1:13" ht="15">
       <c r="A299" s="49">
         <v>130.25897242741709</v>
       </c>
@@ -38947,7 +38947,7 @@
         <v>9.9631027905899181</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="14.25">
+    <row r="300" spans="1:13" ht="15">
       <c r="A300" s="49">
         <v>134.40830260529381</v>
       </c>
@@ -38985,7 +38985,7 @@
         <v>9.1315075306601106</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="14.25">
+    <row r="301" spans="1:13" ht="15">
       <c r="A301" s="49">
         <v>140.087385836701</v>
       </c>
@@ -39023,7 +39023,7 @@
         <v>8.2973888055407734</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="14.25">
+    <row r="302" spans="1:13" ht="15">
       <c r="A302" s="49">
         <v>139.20752787127171</v>
       </c>
@@ -39061,7 +39061,7 @@
         <v>7.474660804413527</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="14.25">
+    <row r="303" spans="1:13" ht="15">
       <c r="A303" s="49">
         <v>139.37750043277512</v>
       </c>
@@ -39099,7 +39099,7 @@
         <v>6.6756356711474174</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="14.25">
+    <row r="304" spans="1:13" ht="15">
       <c r="A304" s="49">
         <v>138.82758920438181</v>
       </c>
@@ -39137,7 +39137,7 @@
         <v>5.9107807836421182</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="14.25">
+    <row r="305" spans="1:13" ht="15">
       <c r="A305" s="49">
         <v>135.2681637987815</v>
       </c>
@@ -39175,7 +39175,7 @@
         <v>5.1885758234463175</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="14.25">
+    <row r="306" spans="1:13" ht="15">
       <c r="A306" s="49">
         <v>131.11883362090478</v>
       </c>
@@ -39213,7 +39213,7 @@
         <v>4.5154659480553212</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="14.25">
+    <row r="307" spans="1:13" ht="15">
       <c r="A307" s="49">
         <v>132.77856569205548</v>
       </c>
@@ -39251,7 +39251,7 @@
         <v>3.8959023625956886</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="14.25">
+    <row r="308" spans="1:13" ht="15">
       <c r="A308" s="49">
         <v>133.5484414118061</v>
       </c>
@@ -39289,7 +39289,7 @@
         <v>3.3324577027114159</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="14.25">
+    <row r="309" spans="1:13" ht="15">
       <c r="A309" s="49">
         <v>129.81904344470243</v>
       </c>
@@ -39327,7 +39327,7 @@
         <v>2.8260010331662024</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="14.25">
+    <row r="310" spans="1:13" ht="15">
       <c r="A310" s="49">
         <v>128.65923067209113</v>
       </c>
@@ -39365,7 +39365,7 @@
         <v>2.3759159640415612</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="14.25">
+    <row r="311" spans="1:13" ht="15">
       <c r="A311" s="49">
         <v>124.80985207333799</v>
       </c>
@@ -39403,7 +39403,7 @@
         <v>1.9803453083965132</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="14.25">
+    <row r="312" spans="1:13" ht="15">
       <c r="A312" s="49">
         <v>118.63084954339143</v>
       </c>
@@ -39441,7 +39441,7 @@
         <v>1.6364466858625928</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="14.25">
+    <row r="313" spans="1:13" ht="15">
       <c r="A313" s="49">
         <v>116.64117073520475</v>
       </c>
@@ -39479,7 +39479,7 @@
         <v>1.3406452903428223</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="14.25">
+    <row r="314" spans="1:13" ht="15">
       <c r="A314" s="49">
         <v>120.05062035124323</v>
       </c>
@@ -39517,7 +39517,7 @@
         <v>1.088872429933041</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="14.25">
+    <row r="315" spans="1:13" ht="15">
       <c r="A315" s="49">
         <v>124.62988112586383</v>
       </c>
@@ -39555,7 +39555,7 @@
         <v>0.87678115217937347</v>
       </c>
     </row>
-    <row r="316" spans="1:13" ht="14.25">
+    <row r="316" spans="1:13" ht="15">
       <c r="A316" s="49">
         <v>123.68003445863903</v>
       </c>
@@ -39593,7 +39593,7 @@
         <v>0.69993304531485256</v>
       </c>
     </row>
-    <row r="317" spans="1:13" ht="14.25">
+    <row r="317" spans="1:13" ht="15">
       <c r="A317" s="49">
         <v>128.96918063718553</v>
       </c>
@@ -39631,7 +39631,7 @@
         <v>0.55395294989054411</v>
       </c>
     </row>
-    <row r="318" spans="1:13" ht="14.25">
+    <row r="318" spans="1:13" ht="15">
       <c r="A318" s="49">
         <v>118.40088666606333</v>
       </c>
@@ -39669,7 +39669,7 @@
         <v>0.4346506663069043</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="14.25">
+    <row r="319" spans="1:13" ht="15">
       <c r="A319" s="49">
         <v>142.59698071536863</v>
       </c>
@@ -39707,7 +39707,7 @@
         <v>0.33811069537463323</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="14.25">
+    <row r="320" spans="1:13" ht="15">
       <c r="A320" s="49">
         <v>147.19623826193077</v>
       </c>
@@ -39744,7 +39744,7 @@
         <v>0.26075254563547801</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="14.25">
+    <row r="321" spans="1:13" ht="15">
       <c r="A321" s="49">
         <v>147.04626247236897</v>
       </c>
@@ -39781,7 +39781,7 @@
         <v>0.19936517300174683</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="14.65" thickBot="1">
+    <row r="322" spans="1:13" ht="15.75" thickBot="1">
       <c r="A322" s="49">
         <v>140.8072696265977</v>
       </c>
@@ -67491,10 +67491,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6963948-7FD9-4D33-AAA7-BDE5D55568DA}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.1328125" style="1"/>
+    <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -67504,48 +67504,48 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB4E6C4-ACE1-4F55-811C-6D8863FFBCD5}">
   <dimension ref="B15:F61"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="3.265625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="79" style="1" customWidth="1"/>
-    <col min="4" max="4" width="101.1328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1328125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="9.1328125" style="1"/>
-    <col min="9" max="9" width="13.73046875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1328125" style="1"/>
+    <col min="4" max="4" width="101.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="13.7109375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="2:6" ht="13.9">
+    <row r="15" spans="2:6" ht="15">
       <c r="B15" s="86" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C15" s="86" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E15" s="87" t="s">
         <v>1649</v>
       </c>
-      <c r="C15" s="86" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D15" s="76" t="s">
-        <v>1658</v>
-      </c>
-      <c r="E15" s="87" t="s">
+      <c r="F15" s="86" t="s">
         <v>1650</v>
-      </c>
-      <c r="F15" s="86" t="s">
-        <v>1651</v>
       </c>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="77" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C16" s="78" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D16" s="78" t="s">
+        <v>1687</v>
+      </c>
+      <c r="E16" s="79" t="s">
         <v>1612</v>
-      </c>
-      <c r="C16" s="78" t="s">
-        <v>1660</v>
-      </c>
-      <c r="D16" s="78" t="s">
-        <v>1688</v>
-      </c>
-      <c r="E16" s="79" t="s">
-        <v>1613</v>
       </c>
       <c r="F16" s="78">
         <v>45490</v>
@@ -67553,16 +67553,16 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="81" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C17" s="82" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D17" s="82" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E17" s="83" t="s">
         <v>1614</v>
-      </c>
-      <c r="C17" s="82" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D17" s="82" t="s">
-        <v>1689</v>
-      </c>
-      <c r="E17" s="83" t="s">
-        <v>1615</v>
       </c>
       <c r="F17" s="82">
         <v>45462</v>
@@ -67570,16 +67570,16 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="77" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C18" s="78" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D18" s="78" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E18" s="79" t="s">
         <v>1616</v>
-      </c>
-      <c r="C18" s="78" t="s">
-        <v>1662</v>
-      </c>
-      <c r="D18" s="78" t="s">
-        <v>1690</v>
-      </c>
-      <c r="E18" s="79" t="s">
-        <v>1617</v>
       </c>
       <c r="F18" s="78">
         <v>45407</v>
@@ -67587,16 +67587,16 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="81" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C19" s="82" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D19" s="82" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E19" s="83" t="s">
         <v>1618</v>
-      </c>
-      <c r="C19" s="82" t="s">
-        <v>1663</v>
-      </c>
-      <c r="D19" s="82" t="s">
-        <v>1691</v>
-      </c>
-      <c r="E19" s="83" t="s">
-        <v>1619</v>
       </c>
       <c r="F19" s="82">
         <v>45406</v>
@@ -67604,16 +67604,16 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="77" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="C20" s="78" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="D20" s="78" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F20" s="78">
         <v>44958</v>
@@ -67621,16 +67621,16 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="81" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="C21" s="82" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="D21" s="82" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="E21" s="83" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F21" s="82">
         <v>44682</v>
@@ -67638,16 +67638,16 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="77" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="C22" s="78" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="D22" s="78" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E22" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F22" s="78">
         <v>44627</v>
@@ -67655,16 +67655,16 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="81" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="C23" s="82" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="D23" s="82" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="E23" s="83" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F23" s="82">
         <v>44571</v>
@@ -67672,16 +67672,16 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="77" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="C24" s="78" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="D24" s="78" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="E24" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F24" s="78">
         <v>44326</v>
@@ -67689,16 +67689,16 @@
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="81" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="C25" s="82" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="D25" s="82" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="E25" s="83" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F25" s="82">
         <v>44165</v>
@@ -67706,16 +67706,16 @@
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="77" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="C26" s="78" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="D26" s="78" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="E26" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F26" s="78">
         <v>43955</v>
@@ -67723,16 +67723,16 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="81" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="C27" s="82" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="D27" s="82" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="E27" s="83" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F27" s="82">
         <v>43896</v>
@@ -67740,16 +67740,16 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="77" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="C28" s="78" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="D28" s="78" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="E28" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F28" s="78">
         <v>43816</v>
@@ -67757,16 +67757,16 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="81" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C29" s="82" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D29" s="82" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E29" s="83" t="s">
         <v>1629</v>
-      </c>
-      <c r="C29" s="82" t="s">
-        <v>1673</v>
-      </c>
-      <c r="D29" s="82" t="s">
-        <v>1701</v>
-      </c>
-      <c r="E29" s="83" t="s">
-        <v>1630</v>
       </c>
       <c r="F29" s="82">
         <v>43536</v>
@@ -67774,16 +67774,16 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="77" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C30" s="78" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D30" s="78" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E30" s="79" t="s">
         <v>1631</v>
-      </c>
-      <c r="C30" s="78" t="s">
-        <v>1674</v>
-      </c>
-      <c r="D30" s="78" t="s">
-        <v>1702</v>
-      </c>
-      <c r="E30" s="79" t="s">
-        <v>1632</v>
       </c>
       <c r="F30" s="78">
         <v>42196</v>
@@ -67791,16 +67791,16 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="81" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="C31" s="82" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="D31" s="82" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="E31" s="83" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F31" s="82">
         <v>41484</v>
@@ -67808,16 +67808,16 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="77" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C32" s="78" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D32" s="78" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E32" s="79" t="s">
         <v>1634</v>
-      </c>
-      <c r="C32" s="78" t="s">
-        <v>1676</v>
-      </c>
-      <c r="D32" s="78" t="s">
-        <v>1704</v>
-      </c>
-      <c r="E32" s="79" t="s">
-        <v>1635</v>
       </c>
       <c r="F32" s="78">
         <v>40672</v>
@@ -67825,16 +67825,16 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="81" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="C33" s="82" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="D33" s="82" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E33" s="83" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F33" s="82">
         <v>39591</v>
@@ -67842,16 +67842,16 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="77" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="C34" s="78" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="D34" s="78" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="E34" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F34" s="78">
         <v>39482</v>
@@ -67859,16 +67859,16 @@
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="81" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="C35" s="82" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="D35" s="82" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E35" s="83" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F35" s="82">
         <v>39448</v>
@@ -67876,16 +67876,16 @@
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="77" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="C36" s="78" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="D36" s="78" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E36" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F36" s="78">
         <v>39429</v>
@@ -67893,16 +67893,16 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="81" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C37" s="82" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D37" s="82" t="s">
+        <v>1708</v>
+      </c>
+      <c r="E37" s="83" t="s">
         <v>1640</v>
-      </c>
-      <c r="C37" s="82" t="s">
-        <v>1681</v>
-      </c>
-      <c r="D37" s="82" t="s">
-        <v>1709</v>
-      </c>
-      <c r="E37" s="83" t="s">
-        <v>1641</v>
       </c>
       <c r="F37" s="82">
         <v>39027</v>
@@ -67910,16 +67910,16 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="77" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="C38" s="78" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="D38" s="78" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="E38" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F38" s="78">
         <v>38798</v>
@@ -67927,16 +67927,16 @@
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="81" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="C39" s="82" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="D39" s="82" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E39" s="83" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F39" s="82">
         <v>38700</v>
@@ -67944,16 +67944,16 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="77" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="C40" s="78" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="E40" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F40" s="78">
         <v>38100</v>
@@ -67961,16 +67961,16 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="81" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C41" s="82" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D41" s="82" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E41" s="83" t="s">
         <v>1645</v>
-      </c>
-      <c r="C41" s="82" t="s">
-        <v>1685</v>
-      </c>
-      <c r="D41" s="82" t="s">
-        <v>1713</v>
-      </c>
-      <c r="E41" s="83" t="s">
-        <v>1646</v>
       </c>
       <c r="F41" s="82">
         <v>37837</v>
@@ -67978,16 +67978,16 @@
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="77" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="C42" s="78" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D42" s="78" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E42" s="79" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F42" s="78">
         <v>37825</v>
@@ -67995,16 +67995,16 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="81" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="C43" s="82" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="D43" s="82" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E43" s="83" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F43" s="82">
         <v>36861</v>
@@ -68144,10 +68144,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD36E60-677E-467E-9C59-7853ADE8E695}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.1328125" style="1"/>
+    <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -68157,13 +68157,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{850CC31F-8910-447E-89B3-28B6120F3B0A}">
   <dimension ref="B2:Z8"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="3.1328125" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.1328125" style="1"/>
+    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" ht="13.9">
+    <row r="2" spans="2:26" ht="15">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -68194,7 +68194,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="6"/>
     </row>
-    <row r="3" spans="2:26" ht="13.9">
+    <row r="3" spans="2:26" ht="15">
       <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
@@ -68225,7 +68225,7 @@
       <c r="Y3" s="10"/>
       <c r="Z3" s="11"/>
     </row>
-    <row r="4" spans="2:26" ht="13.9">
+    <row r="4" spans="2:26" ht="15">
       <c r="B4" s="12" t="s">
         <v>10</v>
       </c>
@@ -68256,7 +68256,7 @@
       <c r="Y4" s="15"/>
       <c r="Z4" s="16"/>
     </row>
-    <row r="5" spans="2:26" ht="13.9">
+    <row r="5" spans="2:26" ht="15">
       <c r="B5" s="12" t="s">
         <v>10</v>
       </c>
@@ -68287,7 +68287,7 @@
       <c r="Y5" s="17"/>
       <c r="Z5" s="18"/>
     </row>
-    <row r="6" spans="2:26" ht="13.9">
+    <row r="6" spans="2:26" ht="15">
       <c r="B6" s="12" t="s">
         <v>10</v>
       </c>
@@ -68318,7 +68318,7 @@
       <c r="Y6" s="15"/>
       <c r="Z6" s="16"/>
     </row>
-    <row r="7" spans="2:26" ht="13.9">
+    <row r="7" spans="2:26" ht="15">
       <c r="B7" s="12" t="s">
         <v>10</v>
       </c>
@@ -68349,7 +68349,7 @@
       <c r="Y7" s="17"/>
       <c r="Z7" s="18"/>
     </row>
-    <row r="8" spans="2:26" ht="13.9">
+    <row r="8" spans="2:26" ht="15">
       <c r="B8" s="19" t="s">
         <v>10</v>
       </c>
